--- a/project-management/skills/pmo-pert-estimate/examples/scenario-4-cloud-migration/pert-estimate.xlsx
+++ b/project-management/skills/pmo-pert-estimate/examples/scenario-4-cloud-migration/pert-estimate.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resources" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
-  <fonts count="8">
+  <numFmts count="0"/>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,19 +41,14 @@
     </font>
     <font/>
     <font>
-      <b val="1"/>
-      <u val="single"/>
-    </font>
-    <font>
       <i val="1"/>
-      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FFFF0000"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,17 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFA500"/>
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,29 +135,16 @@
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5087,1540 +5056,1658 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE78"/>
+  <dimension ref="A1:BB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="6" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="6" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="6" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="6" customWidth="1" min="23" max="23"/>
-    <col width="6" customWidth="1" min="24" max="24"/>
-    <col width="6" customWidth="1" min="25" max="25"/>
-    <col width="6" customWidth="1" min="26" max="26"/>
-    <col width="6" customWidth="1" min="27" max="27"/>
-    <col width="6" customWidth="1" min="28" max="28"/>
-    <col width="6" customWidth="1" min="29" max="29"/>
-    <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="10" customWidth="1" min="53" max="53"/>
+    <col width="14" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Phase/WP/Activity</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>PERT Duration</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>σ</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>P12</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>P23</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>P24</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>P25</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>P26</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P27</t>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="L1" s="14" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="M1" s="14" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="N1" s="14" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="O1" s="14" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="P1" s="14" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="Q1" s="14" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="R1" s="14" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="S1" s="14" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="T1" s="14" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="U1" s="14" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="V1" s="14" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="W1" s="14" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="X1" s="14" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="Y1" s="14" t="inlineStr">
+        <is>
+          <t>W22</t>
+        </is>
+      </c>
+      <c r="Z1" s="14" t="inlineStr">
+        <is>
+          <t>W23</t>
+        </is>
+      </c>
+      <c r="AA1" s="14" t="inlineStr">
+        <is>
+          <t>W24</t>
+        </is>
+      </c>
+      <c r="AB1" s="14" t="inlineStr">
+        <is>
+          <t>W25</t>
+        </is>
+      </c>
+      <c r="AC1" s="14" t="inlineStr">
+        <is>
+          <t>W26</t>
+        </is>
+      </c>
+      <c r="AD1" s="14" t="inlineStr">
+        <is>
+          <t>W27</t>
+        </is>
+      </c>
+      <c r="AE1" s="14" t="inlineStr">
+        <is>
+          <t>W28</t>
+        </is>
+      </c>
+      <c r="AF1" s="14" t="inlineStr">
+        <is>
+          <t>W29</t>
+        </is>
+      </c>
+      <c r="AG1" s="14" t="inlineStr">
+        <is>
+          <t>W30</t>
+        </is>
+      </c>
+      <c r="AH1" s="14" t="inlineStr">
+        <is>
+          <t>W31</t>
+        </is>
+      </c>
+      <c r="AI1" s="14" t="inlineStr">
+        <is>
+          <t>W32</t>
+        </is>
+      </c>
+      <c r="AJ1" s="14" t="inlineStr">
+        <is>
+          <t>W33</t>
+        </is>
+      </c>
+      <c r="AK1" s="14" t="inlineStr">
+        <is>
+          <t>W34</t>
+        </is>
+      </c>
+      <c r="AL1" s="14" t="inlineStr">
+        <is>
+          <t>W35</t>
+        </is>
+      </c>
+      <c r="AM1" s="14" t="inlineStr">
+        <is>
+          <t>W36</t>
+        </is>
+      </c>
+      <c r="AN1" s="14" t="inlineStr">
+        <is>
+          <t>W37</t>
+        </is>
+      </c>
+      <c r="AO1" s="14" t="inlineStr">
+        <is>
+          <t>W38</t>
+        </is>
+      </c>
+      <c r="AP1" s="14" t="inlineStr">
+        <is>
+          <t>W39</t>
+        </is>
+      </c>
+      <c r="AQ1" s="14" t="inlineStr">
+        <is>
+          <t>W40</t>
+        </is>
+      </c>
+      <c r="AR1" s="14" t="inlineStr">
+        <is>
+          <t>W41</t>
+        </is>
+      </c>
+      <c r="AS1" s="14" t="inlineStr">
+        <is>
+          <t>W42</t>
+        </is>
+      </c>
+      <c r="AT1" s="14" t="inlineStr">
+        <is>
+          <t>W43</t>
+        </is>
+      </c>
+      <c r="AU1" s="14" t="inlineStr">
+        <is>
+          <t>W44</t>
+        </is>
+      </c>
+      <c r="AV1" s="14" t="inlineStr">
+        <is>
+          <t>W45</t>
+        </is>
+      </c>
+      <c r="AW1" s="14" t="inlineStr">
+        <is>
+          <t>W46</t>
+        </is>
+      </c>
+      <c r="AX1" s="14" t="inlineStr">
+        <is>
+          <t>W47</t>
+        </is>
+      </c>
+      <c r="AY1" s="14" t="inlineStr">
+        <is>
+          <t>W48</t>
+        </is>
+      </c>
+      <c r="AZ1" s="14" t="inlineStr">
+        <is>
+          <t>W49</t>
+        </is>
+      </c>
+      <c r="BA1" s="14" t="inlineStr">
+        <is>
+          <t>W50</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL (PD)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>WBS!A2</f>
-        <v/>
-      </c>
-      <c r="B2">
-        <f>WBS!B2&amp;IF(WBS!C2&lt;&gt;"", " "&amp;WBS!C2, "")&amp;IF(WBS!D2&lt;&gt;"", " "&amp;WBS!D2, "")</f>
-        <v/>
-      </c>
-      <c r="C2">
-        <f>WBS!L2</f>
-        <v/>
-      </c>
-      <c r="D2">
-        <f>WBS!M2</f>
-        <v/>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Week of</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="I2" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J2" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="M2" s="15" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="N2" s="15" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="O2" s="15" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="P2" s="15" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="Q2" s="15" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="R2" s="15" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="S2" s="15" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="T2" s="15" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+      <c r="U2" s="15" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="V2" s="15" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="W2" s="15" t="inlineStr">
+        <is>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="X2" s="15" t="inlineStr">
+        <is>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="Y2" s="15" t="inlineStr">
+        <is>
+          <t>2027-01-26</t>
+        </is>
+      </c>
+      <c r="Z2" s="15" t="inlineStr">
+        <is>
+          <t>2027-02-02</t>
+        </is>
+      </c>
+      <c r="AA2" s="15" t="inlineStr">
+        <is>
+          <t>2027-02-09</t>
+        </is>
+      </c>
+      <c r="AB2" s="15" t="inlineStr">
+        <is>
+          <t>2027-02-16</t>
+        </is>
+      </c>
+      <c r="AC2" s="15" t="inlineStr">
+        <is>
+          <t>2027-02-23</t>
+        </is>
+      </c>
+      <c r="AD2" s="15" t="inlineStr">
+        <is>
+          <t>2027-03-02</t>
+        </is>
+      </c>
+      <c r="AE2" s="15" t="inlineStr">
+        <is>
+          <t>2027-03-09</t>
+        </is>
+      </c>
+      <c r="AF2" s="15" t="inlineStr">
+        <is>
+          <t>2027-03-16</t>
+        </is>
+      </c>
+      <c r="AG2" s="15" t="inlineStr">
+        <is>
+          <t>2027-03-23</t>
+        </is>
+      </c>
+      <c r="AH2" s="15" t="inlineStr">
+        <is>
+          <t>2027-03-30</t>
+        </is>
+      </c>
+      <c r="AI2" s="15" t="inlineStr">
+        <is>
+          <t>2027-04-06</t>
+        </is>
+      </c>
+      <c r="AJ2" s="15" t="inlineStr">
+        <is>
+          <t>2027-04-13</t>
+        </is>
+      </c>
+      <c r="AK2" s="15" t="inlineStr">
+        <is>
+          <t>2027-04-20</t>
+        </is>
+      </c>
+      <c r="AL2" s="15" t="inlineStr">
+        <is>
+          <t>2027-04-27</t>
+        </is>
+      </c>
+      <c r="AM2" s="15" t="inlineStr">
+        <is>
+          <t>2027-05-04</t>
+        </is>
+      </c>
+      <c r="AN2" s="15" t="inlineStr">
+        <is>
+          <t>2027-05-11</t>
+        </is>
+      </c>
+      <c r="AO2" s="15" t="inlineStr">
+        <is>
+          <t>2027-05-18</t>
+        </is>
+      </c>
+      <c r="AP2" s="15" t="inlineStr">
+        <is>
+          <t>2027-05-25</t>
+        </is>
+      </c>
+      <c r="AQ2" s="15" t="inlineStr">
+        <is>
+          <t>2027-06-01</t>
+        </is>
+      </c>
+      <c r="AR2" s="15" t="inlineStr">
+        <is>
+          <t>2027-06-08</t>
+        </is>
+      </c>
+      <c r="AS2" s="15" t="inlineStr">
+        <is>
+          <t>2027-06-15</t>
+        </is>
+      </c>
+      <c r="AT2" s="15" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="AU2" s="15" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="AV2" s="15" t="inlineStr">
+        <is>
+          <t>2027-07-06</t>
+        </is>
+      </c>
+      <c r="AW2" s="15" t="inlineStr">
+        <is>
+          <t>2027-07-13</t>
+        </is>
+      </c>
+      <c r="AX2" s="15" t="inlineStr">
+        <is>
+          <t>2027-07-20</t>
+        </is>
+      </c>
+      <c r="AY2" s="15" t="inlineStr">
+        <is>
+          <t>2027-07-27</t>
+        </is>
+      </c>
+      <c r="AZ2" s="15" t="inlineStr">
+        <is>
+          <t>2027-08-03</t>
+        </is>
+      </c>
+      <c r="BA2" s="15" t="inlineStr">
+        <is>
+          <t>2027-08-10</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <f>WBS!A3</f>
-        <v/>
-      </c>
-      <c r="B3">
-        <f>WBS!B3&amp;IF(WBS!C3&lt;&gt;"", " "&amp;WBS!C3, "")&amp;IF(WBS!D3&lt;&gt;"", " "&amp;WBS!D3, "")</f>
-        <v/>
-      </c>
-      <c r="C3">
-        <f>WBS!L3</f>
-        <v/>
-      </c>
-      <c r="D3">
-        <f>WBS!M3</f>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>billable</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I3" s="16" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="J3" s="16" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="K3" s="16" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="L3" s="16" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="M3" s="16" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="N3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AM3" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AN3" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AO3" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP3" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ3" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR3" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AS3" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT3" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AU3" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="18">
+        <f>SUM(D3:BA3)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <f>WBS!A4</f>
-        <v/>
-      </c>
-      <c r="B4">
-        <f>WBS!B4&amp;IF(WBS!C4&lt;&gt;"", " "&amp;WBS!C4, "")&amp;IF(WBS!D4&lt;&gt;"", " "&amp;WBS!D4, "")</f>
-        <v/>
-      </c>
-      <c r="C4">
-        <f>WBS!L4</f>
-        <v/>
-      </c>
-      <c r="D4">
-        <f>WBS!M4</f>
-        <v/>
-      </c>
-      <c r="E4" s="14" t="n"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>billable</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K4" s="17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L4" s="17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M4" s="17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N4" s="16" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="O4" s="16" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="P4" s="16" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q4" s="16" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="R4" s="16" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="S4" s="16" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T4" s="16" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U4" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V4" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W4" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X4" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Y4" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z4" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA4" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB4" s="17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC4" s="17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD4" s="17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE4" s="17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF4" s="17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG4" s="17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH4" s="17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI4" s="17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ4" s="17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK4" s="17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL4" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AM4" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN4" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO4" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP4" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ4" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR4" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS4" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT4" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU4" s="17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AV4" s="17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AW4" s="17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AX4" s="17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AY4" s="17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AZ4" s="17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BA4" s="17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BB4" s="18">
+        <f>SUM(D4:BA4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <f>WBS!A5</f>
-        <v/>
-      </c>
-      <c r="B5">
-        <f>WBS!B5&amp;IF(WBS!C5&lt;&gt;"", " "&amp;WBS!C5, "")&amp;IF(WBS!D5&lt;&gt;"", " "&amp;WBS!D5, "")</f>
-        <v/>
-      </c>
-      <c r="C5">
-        <f>WBS!L5</f>
-        <v/>
-      </c>
-      <c r="D5">
-        <f>WBS!M5</f>
-        <v/>
-      </c>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="n"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>billable</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="V5" s="17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W5" s="17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="X5" s="17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y5" s="17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Z5" s="17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AA5" s="17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB5" s="17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AC5" s="17" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AD5" s="17" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AE5" s="17" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AF5" s="17" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AG5" s="17" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AH5" s="17" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AI5" s="17" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AJ5" s="17" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AK5" s="17" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AL5" s="16" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AM5" s="16" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AN5" s="16" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AO5" s="16" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AP5" s="16" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AQ5" s="16" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AR5" s="16" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AS5" s="16" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AT5" s="16" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AU5" s="16" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AV5" s="17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AW5" s="17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AX5" s="17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AY5" s="17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ5" s="17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BA5" s="17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BB5" s="18">
+        <f>SUM(D5:BA5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <f>WBS!A6</f>
-        <v/>
-      </c>
-      <c r="B6">
-        <f>WBS!B6&amp;IF(WBS!C6&lt;&gt;"", " "&amp;WBS!C6, "")&amp;IF(WBS!D6&lt;&gt;"", " "&amp;WBS!D6, "")</f>
-        <v/>
-      </c>
-      <c r="C6">
-        <f>WBS!L6</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>WBS!M6</f>
-        <v/>
-      </c>
-      <c r="E6" s="15" t="n"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>billable</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AW6" s="17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX6" s="17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY6" s="17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AZ6" s="17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BA6" s="17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB6" s="18">
+        <f>SUM(D6:BA6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <f>WBS!A7</f>
-        <v/>
-      </c>
-      <c r="B7">
-        <f>WBS!B7&amp;IF(WBS!C7&lt;&gt;"", " "&amp;WBS!C7, "")&amp;IF(WBS!D7&lt;&gt;"", " "&amp;WBS!D7, "")</f>
-        <v/>
-      </c>
-      <c r="C7">
-        <f>WBS!L7</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>WBS!M7</f>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>billable</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M7" s="17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N7" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O7" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P7" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q7" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R7" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S7" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T7" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="U7" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="V7" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="W7" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="X7" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Y7" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Z7" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AA7" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB7" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AC7" s="17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AD7" s="17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AE7" s="17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AF7" s="17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AG7" s="17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AH7" s="17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AI7" s="17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AJ7" s="17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AK7" s="17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AL7" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AM7" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AN7" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AO7" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AP7" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AQ7" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AR7" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AS7" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AT7" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AU7" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AV7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="18">
+        <f>SUM(D7:BA7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <f>WBS!A8</f>
-        <v/>
-      </c>
-      <c r="B8">
-        <f>WBS!B8&amp;IF(WBS!C8&lt;&gt;"", " "&amp;WBS!C8, "")&amp;IF(WBS!D8&lt;&gt;"", " "&amp;WBS!D8, "")</f>
-        <v/>
-      </c>
-      <c r="C8">
-        <f>WBS!L8</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>WBS!M8</f>
-        <v/>
-      </c>
-      <c r="F8" s="14" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <f>WBS!A9</f>
-        <v/>
-      </c>
-      <c r="B9">
-        <f>WBS!B9&amp;IF(WBS!C9&lt;&gt;"", " "&amp;WBS!C9, "")&amp;IF(WBS!D9&lt;&gt;"", " "&amp;WBS!D9, "")</f>
-        <v/>
-      </c>
-      <c r="C9">
-        <f>WBS!L9</f>
-        <v/>
-      </c>
-      <c r="D9">
-        <f>WBS!M9</f>
-        <v/>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <f>WBS!A10</f>
-        <v/>
-      </c>
-      <c r="B10">
-        <f>WBS!B10&amp;IF(WBS!C10&lt;&gt;"", " "&amp;WBS!C10, "")&amp;IF(WBS!D10&lt;&gt;"", " "&amp;WBS!D10, "")</f>
-        <v/>
-      </c>
-      <c r="C10">
-        <f>WBS!L10</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>WBS!M10</f>
-        <v/>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <f>WBS!A11</f>
-        <v/>
-      </c>
-      <c r="B11">
-        <f>WBS!B11&amp;IF(WBS!C11&lt;&gt;"", " "&amp;WBS!C11, "")&amp;IF(WBS!D11&lt;&gt;"", " "&amp;WBS!D11, "")</f>
-        <v/>
-      </c>
-      <c r="C11">
-        <f>WBS!L11</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>WBS!M11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <f>WBS!A12</f>
-        <v/>
-      </c>
-      <c r="B12">
-        <f>WBS!B12&amp;IF(WBS!C12&lt;&gt;"", " "&amp;WBS!C12, "")&amp;IF(WBS!D12&lt;&gt;"", " "&amp;WBS!D12, "")</f>
-        <v/>
-      </c>
-      <c r="C12">
-        <f>WBS!L12</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>WBS!M12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <f>WBS!A13</f>
-        <v/>
-      </c>
-      <c r="B13">
-        <f>WBS!B13&amp;IF(WBS!C13&lt;&gt;"", " "&amp;WBS!C13, "")&amp;IF(WBS!D13&lt;&gt;"", " "&amp;WBS!D13, "")</f>
-        <v/>
-      </c>
-      <c r="C13">
-        <f>WBS!L13</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>WBS!M13</f>
-        <v/>
-      </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <f>WBS!A14</f>
-        <v/>
-      </c>
-      <c r="B14">
-        <f>WBS!B14&amp;IF(WBS!C14&lt;&gt;"", " "&amp;WBS!C14, "")&amp;IF(WBS!D14&lt;&gt;"", " "&amp;WBS!D14, "")</f>
-        <v/>
-      </c>
-      <c r="C14">
-        <f>WBS!L14</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>WBS!M14</f>
-        <v/>
-      </c>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <f>WBS!A15</f>
-        <v/>
-      </c>
-      <c r="B15">
-        <f>WBS!B15&amp;IF(WBS!C15&lt;&gt;"", " "&amp;WBS!C15, "")&amp;IF(WBS!D15&lt;&gt;"", " "&amp;WBS!D15, "")</f>
-        <v/>
-      </c>
-      <c r="C15">
-        <f>WBS!L15</f>
-        <v/>
-      </c>
-      <c r="D15">
-        <f>WBS!M15</f>
-        <v/>
-      </c>
-      <c r="H15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <f>WBS!A16</f>
-        <v/>
-      </c>
-      <c r="B16">
-        <f>WBS!B16&amp;IF(WBS!C16&lt;&gt;"", " "&amp;WBS!C16, "")&amp;IF(WBS!D16&lt;&gt;"", " "&amp;WBS!D16, "")</f>
-        <v/>
-      </c>
-      <c r="C16">
-        <f>WBS!L16</f>
-        <v/>
-      </c>
-      <c r="D16">
-        <f>WBS!M16</f>
-        <v/>
-      </c>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <f>WBS!A17</f>
-        <v/>
-      </c>
-      <c r="B17">
-        <f>WBS!B17&amp;IF(WBS!C17&lt;&gt;"", " "&amp;WBS!C17, "")&amp;IF(WBS!D17&lt;&gt;"", " "&amp;WBS!D17, "")</f>
-        <v/>
-      </c>
-      <c r="C17">
-        <f>WBS!L17</f>
-        <v/>
-      </c>
-      <c r="D17">
-        <f>WBS!M17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <f>WBS!A18</f>
-        <v/>
-      </c>
-      <c r="B18">
-        <f>WBS!B18&amp;IF(WBS!C18&lt;&gt;"", " "&amp;WBS!C18, "")&amp;IF(WBS!D18&lt;&gt;"", " "&amp;WBS!D18, "")</f>
-        <v/>
-      </c>
-      <c r="C18">
-        <f>WBS!L18</f>
-        <v/>
-      </c>
-      <c r="D18">
-        <f>WBS!M18</f>
-        <v/>
-      </c>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <f>WBS!A19</f>
-        <v/>
-      </c>
-      <c r="B19">
-        <f>WBS!B19&amp;IF(WBS!C19&lt;&gt;"", " "&amp;WBS!C19, "")&amp;IF(WBS!D19&lt;&gt;"", " "&amp;WBS!D19, "")</f>
-        <v/>
-      </c>
-      <c r="C19">
-        <f>WBS!L19</f>
-        <v/>
-      </c>
-      <c r="D19">
-        <f>WBS!M19</f>
-        <v/>
-      </c>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <f>WBS!A20</f>
-        <v/>
-      </c>
-      <c r="B20">
-        <f>WBS!B20&amp;IF(WBS!C20&lt;&gt;"", " "&amp;WBS!C20, "")&amp;IF(WBS!D20&lt;&gt;"", " "&amp;WBS!D20, "")</f>
-        <v/>
-      </c>
-      <c r="C20">
-        <f>WBS!L20</f>
-        <v/>
-      </c>
-      <c r="D20">
-        <f>WBS!M20</f>
-        <v/>
-      </c>
-      <c r="I20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <f>WBS!A21</f>
-        <v/>
-      </c>
-      <c r="B21">
-        <f>WBS!B21&amp;IF(WBS!C21&lt;&gt;"", " "&amp;WBS!C21, "")&amp;IF(WBS!D21&lt;&gt;"", " "&amp;WBS!D21, "")</f>
-        <v/>
-      </c>
-      <c r="C21">
-        <f>WBS!L21</f>
-        <v/>
-      </c>
-      <c r="D21">
-        <f>WBS!M21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <f>WBS!A22</f>
-        <v/>
-      </c>
-      <c r="B22">
-        <f>WBS!B22&amp;IF(WBS!C22&lt;&gt;"", " "&amp;WBS!C22, "")&amp;IF(WBS!D22&lt;&gt;"", " "&amp;WBS!D22, "")</f>
-        <v/>
-      </c>
-      <c r="C22">
-        <f>WBS!L22</f>
-        <v/>
-      </c>
-      <c r="D22">
-        <f>WBS!M22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <f>WBS!A23</f>
-        <v/>
-      </c>
-      <c r="B23">
-        <f>WBS!B23&amp;IF(WBS!C23&lt;&gt;"", " "&amp;WBS!C23, "")&amp;IF(WBS!D23&lt;&gt;"", " "&amp;WBS!D23, "")</f>
-        <v/>
-      </c>
-      <c r="C23">
-        <f>WBS!L23</f>
-        <v/>
-      </c>
-      <c r="D23">
-        <f>WBS!M23</f>
-        <v/>
-      </c>
-      <c r="H23" s="14" t="n"/>
-      <c r="I23" s="14" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <f>WBS!A24</f>
-        <v/>
-      </c>
-      <c r="B24">
-        <f>WBS!B24&amp;IF(WBS!C24&lt;&gt;"", " "&amp;WBS!C24, "")&amp;IF(WBS!D24&lt;&gt;"", " "&amp;WBS!D24, "")</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>WBS!L24</f>
-        <v/>
-      </c>
-      <c r="D24">
-        <f>WBS!M24</f>
-        <v/>
-      </c>
-      <c r="I24" s="14" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <f>WBS!A25</f>
-        <v/>
-      </c>
-      <c r="B25">
-        <f>WBS!B25&amp;IF(WBS!C25&lt;&gt;"", " "&amp;WBS!C25, "")&amp;IF(WBS!D25&lt;&gt;"", " "&amp;WBS!D25, "")</f>
-        <v/>
-      </c>
-      <c r="C25">
-        <f>WBS!L25</f>
-        <v/>
-      </c>
-      <c r="D25">
-        <f>WBS!M25</f>
-        <v/>
-      </c>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <f>WBS!A26</f>
-        <v/>
-      </c>
-      <c r="B26">
-        <f>WBS!B26&amp;IF(WBS!C26&lt;&gt;"", " "&amp;WBS!C26, "")&amp;IF(WBS!D26&lt;&gt;"", " "&amp;WBS!D26, "")</f>
-        <v/>
-      </c>
-      <c r="C26">
-        <f>WBS!L26</f>
-        <v/>
-      </c>
-      <c r="D26">
-        <f>WBS!M26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <f>WBS!A27</f>
-        <v/>
-      </c>
-      <c r="B27">
-        <f>WBS!B27&amp;IF(WBS!C27&lt;&gt;"", " "&amp;WBS!C27, "")&amp;IF(WBS!D27&lt;&gt;"", " "&amp;WBS!D27, "")</f>
-        <v/>
-      </c>
-      <c r="C27">
-        <f>WBS!L27</f>
-        <v/>
-      </c>
-      <c r="D27">
-        <f>WBS!M27</f>
-        <v/>
-      </c>
-      <c r="I27" s="14" t="n"/>
-      <c r="J27" s="14" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <f>WBS!A28</f>
-        <v/>
-      </c>
-      <c r="B28">
-        <f>WBS!B28&amp;IF(WBS!C28&lt;&gt;"", " "&amp;WBS!C28, "")&amp;IF(WBS!D28&lt;&gt;"", " "&amp;WBS!D28, "")</f>
-        <v/>
-      </c>
-      <c r="C28">
-        <f>WBS!L28</f>
-        <v/>
-      </c>
-      <c r="D28">
-        <f>WBS!M28</f>
-        <v/>
-      </c>
-      <c r="J28" s="14" t="n"/>
-      <c r="K28" s="14" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <f>WBS!A29</f>
-        <v/>
-      </c>
-      <c r="B29">
-        <f>WBS!B29&amp;IF(WBS!C29&lt;&gt;"", " "&amp;WBS!C29, "")&amp;IF(WBS!D29&lt;&gt;"", " "&amp;WBS!D29, "")</f>
-        <v/>
-      </c>
-      <c r="C29">
-        <f>WBS!L29</f>
-        <v/>
-      </c>
-      <c r="D29">
-        <f>WBS!M29</f>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="n"/>
-      <c r="K29" s="15" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <f>WBS!A30</f>
-        <v/>
-      </c>
-      <c r="B30">
-        <f>WBS!B30&amp;IF(WBS!C30&lt;&gt;"", " "&amp;WBS!C30, "")&amp;IF(WBS!D30&lt;&gt;"", " "&amp;WBS!D30, "")</f>
-        <v/>
-      </c>
-      <c r="C30">
-        <f>WBS!L30</f>
-        <v/>
-      </c>
-      <c r="D30">
-        <f>WBS!M30</f>
-        <v/>
-      </c>
-      <c r="I30" s="15" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <f>WBS!A31</f>
-        <v/>
-      </c>
-      <c r="B31">
-        <f>WBS!B31&amp;IF(WBS!C31&lt;&gt;"", " "&amp;WBS!C31, "")&amp;IF(WBS!D31&lt;&gt;"", " "&amp;WBS!D31, "")</f>
-        <v/>
-      </c>
-      <c r="C31">
-        <f>WBS!L31</f>
-        <v/>
-      </c>
-      <c r="D31">
-        <f>WBS!M31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <f>WBS!A32</f>
-        <v/>
-      </c>
-      <c r="B32">
-        <f>WBS!B32&amp;IF(WBS!C32&lt;&gt;"", " "&amp;WBS!C32, "")&amp;IF(WBS!D32&lt;&gt;"", " "&amp;WBS!D32, "")</f>
-        <v/>
-      </c>
-      <c r="C32">
-        <f>WBS!L32</f>
-        <v/>
-      </c>
-      <c r="D32">
-        <f>WBS!M32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <f>WBS!A33</f>
-        <v/>
-      </c>
-      <c r="B33">
-        <f>WBS!B33&amp;IF(WBS!C33&lt;&gt;"", " "&amp;WBS!C33, "")&amp;IF(WBS!D33&lt;&gt;"", " "&amp;WBS!D33, "")</f>
-        <v/>
-      </c>
-      <c r="C33">
-        <f>WBS!L33</f>
-        <v/>
-      </c>
-      <c r="D33">
-        <f>WBS!M33</f>
-        <v/>
-      </c>
-      <c r="K33" s="14" t="n"/>
-      <c r="L33" s="14" t="n"/>
-      <c r="M33" s="14" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <f>WBS!A34</f>
-        <v/>
-      </c>
-      <c r="B34">
-        <f>WBS!B34&amp;IF(WBS!C34&lt;&gt;"", " "&amp;WBS!C34, "")&amp;IF(WBS!D34&lt;&gt;"", " "&amp;WBS!D34, "")</f>
-        <v/>
-      </c>
-      <c r="C34">
-        <f>WBS!L34</f>
-        <v/>
-      </c>
-      <c r="D34">
-        <f>WBS!M34</f>
-        <v/>
-      </c>
-      <c r="M34" s="14" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <f>WBS!A35</f>
-        <v/>
-      </c>
-      <c r="B35">
-        <f>WBS!B35&amp;IF(WBS!C35&lt;&gt;"", " "&amp;WBS!C35, "")&amp;IF(WBS!D35&lt;&gt;"", " "&amp;WBS!D35, "")</f>
-        <v/>
-      </c>
-      <c r="C35">
-        <f>WBS!L35</f>
-        <v/>
-      </c>
-      <c r="D35">
-        <f>WBS!M35</f>
-        <v/>
-      </c>
-      <c r="M35" s="14" t="n"/>
-      <c r="N35" s="14" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <f>WBS!A36</f>
-        <v/>
-      </c>
-      <c r="B36">
-        <f>WBS!B36&amp;IF(WBS!C36&lt;&gt;"", " "&amp;WBS!C36, "")&amp;IF(WBS!D36&lt;&gt;"", " "&amp;WBS!D36, "")</f>
-        <v/>
-      </c>
-      <c r="C36">
-        <f>WBS!L36</f>
-        <v/>
-      </c>
-      <c r="D36">
-        <f>WBS!M36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <f>WBS!A37</f>
-        <v/>
-      </c>
-      <c r="B37">
-        <f>WBS!B37&amp;IF(WBS!C37&lt;&gt;"", " "&amp;WBS!C37, "")&amp;IF(WBS!D37&lt;&gt;"", " "&amp;WBS!D37, "")</f>
-        <v/>
-      </c>
-      <c r="C37">
-        <f>WBS!L37</f>
-        <v/>
-      </c>
-      <c r="D37">
-        <f>WBS!M37</f>
-        <v/>
-      </c>
-      <c r="N37" s="14" t="n"/>
-      <c r="O37" s="14" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <f>WBS!A38</f>
-        <v/>
-      </c>
-      <c r="B38">
-        <f>WBS!B38&amp;IF(WBS!C38&lt;&gt;"", " "&amp;WBS!C38, "")&amp;IF(WBS!D38&lt;&gt;"", " "&amp;WBS!D38, "")</f>
-        <v/>
-      </c>
-      <c r="C38">
-        <f>WBS!L38</f>
-        <v/>
-      </c>
-      <c r="D38">
-        <f>WBS!M38</f>
-        <v/>
-      </c>
-      <c r="O38" s="15" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <f>WBS!A39</f>
-        <v/>
-      </c>
-      <c r="B39">
-        <f>WBS!B39&amp;IF(WBS!C39&lt;&gt;"", " "&amp;WBS!C39, "")&amp;IF(WBS!D39&lt;&gt;"", " "&amp;WBS!D39, "")</f>
-        <v/>
-      </c>
-      <c r="C39">
-        <f>WBS!L39</f>
-        <v/>
-      </c>
-      <c r="D39">
-        <f>WBS!M39</f>
-        <v/>
-      </c>
-      <c r="O39" s="14" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <f>WBS!A40</f>
-        <v/>
-      </c>
-      <c r="B40">
-        <f>WBS!B40&amp;IF(WBS!C40&lt;&gt;"", " "&amp;WBS!C40, "")&amp;IF(WBS!D40&lt;&gt;"", " "&amp;WBS!D40, "")</f>
-        <v/>
-      </c>
-      <c r="C40">
-        <f>WBS!L40</f>
-        <v/>
-      </c>
-      <c r="D40">
-        <f>WBS!M40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <f>WBS!A41</f>
-        <v/>
-      </c>
-      <c r="B41">
-        <f>WBS!B41&amp;IF(WBS!C41&lt;&gt;"", " "&amp;WBS!C41, "")&amp;IF(WBS!D41&lt;&gt;"", " "&amp;WBS!D41, "")</f>
-        <v/>
-      </c>
-      <c r="C41">
-        <f>WBS!L41</f>
-        <v/>
-      </c>
-      <c r="D41">
-        <f>WBS!M41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <f>WBS!A42</f>
-        <v/>
-      </c>
-      <c r="B42">
-        <f>WBS!B42&amp;IF(WBS!C42&lt;&gt;"", " "&amp;WBS!C42, "")&amp;IF(WBS!D42&lt;&gt;"", " "&amp;WBS!D42, "")</f>
-        <v/>
-      </c>
-      <c r="C42">
-        <f>WBS!L42</f>
-        <v/>
-      </c>
-      <c r="D42">
-        <f>WBS!M42</f>
-        <v/>
-      </c>
-      <c r="O42" s="14" t="n"/>
-      <c r="P42" s="14" t="n"/>
-      <c r="Q42" s="14" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <f>WBS!A43</f>
-        <v/>
-      </c>
-      <c r="B43">
-        <f>WBS!B43&amp;IF(WBS!C43&lt;&gt;"", " "&amp;WBS!C43, "")&amp;IF(WBS!D43&lt;&gt;"", " "&amp;WBS!D43, "")</f>
-        <v/>
-      </c>
-      <c r="C43">
-        <f>WBS!L43</f>
-        <v/>
-      </c>
-      <c r="D43">
-        <f>WBS!M43</f>
-        <v/>
-      </c>
-      <c r="Q43" s="14" t="n"/>
-      <c r="R43" s="14" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>WBS!A44</f>
-        <v/>
-      </c>
-      <c r="B44">
-        <f>WBS!B44&amp;IF(WBS!C44&lt;&gt;"", " "&amp;WBS!C44, "")&amp;IF(WBS!D44&lt;&gt;"", " "&amp;WBS!D44, "")</f>
-        <v/>
-      </c>
-      <c r="C44">
-        <f>WBS!L44</f>
-        <v/>
-      </c>
-      <c r="D44">
-        <f>WBS!M44</f>
-        <v/>
-      </c>
-      <c r="R44" s="14" t="n"/>
-      <c r="S44" s="14" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <f>WBS!A45</f>
-        <v/>
-      </c>
-      <c r="B45">
-        <f>WBS!B45&amp;IF(WBS!C45&lt;&gt;"", " "&amp;WBS!C45, "")&amp;IF(WBS!D45&lt;&gt;"", " "&amp;WBS!D45, "")</f>
-        <v/>
-      </c>
-      <c r="C45">
-        <f>WBS!L45</f>
-        <v/>
-      </c>
-      <c r="D45">
-        <f>WBS!M45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <f>WBS!A46</f>
-        <v/>
-      </c>
-      <c r="B46">
-        <f>WBS!B46&amp;IF(WBS!C46&lt;&gt;"", " "&amp;WBS!C46, "")&amp;IF(WBS!D46&lt;&gt;"", " "&amp;WBS!D46, "")</f>
-        <v/>
-      </c>
-      <c r="C46">
-        <f>WBS!L46</f>
-        <v/>
-      </c>
-      <c r="D46">
-        <f>WBS!M46</f>
-        <v/>
-      </c>
-      <c r="S46" s="14" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <f>WBS!A47</f>
-        <v/>
-      </c>
-      <c r="B47">
-        <f>WBS!B47&amp;IF(WBS!C47&lt;&gt;"", " "&amp;WBS!C47, "")&amp;IF(WBS!D47&lt;&gt;"", " "&amp;WBS!D47, "")</f>
-        <v/>
-      </c>
-      <c r="C47">
-        <f>WBS!L47</f>
-        <v/>
-      </c>
-      <c r="D47">
-        <f>WBS!M47</f>
-        <v/>
-      </c>
-      <c r="T47" s="15" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <f>WBS!A48</f>
-        <v/>
-      </c>
-      <c r="B48">
-        <f>WBS!B48&amp;IF(WBS!C48&lt;&gt;"", " "&amp;WBS!C48, "")&amp;IF(WBS!D48&lt;&gt;"", " "&amp;WBS!D48, "")</f>
-        <v/>
-      </c>
-      <c r="C48">
-        <f>WBS!L48</f>
-        <v/>
-      </c>
-      <c r="D48">
-        <f>WBS!M48</f>
-        <v/>
-      </c>
-      <c r="T48" s="14" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <f>WBS!A49</f>
-        <v/>
-      </c>
-      <c r="B49">
-        <f>WBS!B49&amp;IF(WBS!C49&lt;&gt;"", " "&amp;WBS!C49, "")&amp;IF(WBS!D49&lt;&gt;"", " "&amp;WBS!D49, "")</f>
-        <v/>
-      </c>
-      <c r="C49">
-        <f>WBS!L49</f>
-        <v/>
-      </c>
-      <c r="D49">
-        <f>WBS!M49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <f>WBS!A50</f>
-        <v/>
-      </c>
-      <c r="B50">
-        <f>WBS!B50&amp;IF(WBS!C50&lt;&gt;"", " "&amp;WBS!C50, "")&amp;IF(WBS!D50&lt;&gt;"", " "&amp;WBS!D50, "")</f>
-        <v/>
-      </c>
-      <c r="C50">
-        <f>WBS!L50</f>
-        <v/>
-      </c>
-      <c r="D50">
-        <f>WBS!M50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <f>WBS!A51</f>
-        <v/>
-      </c>
-      <c r="B51">
-        <f>WBS!B51&amp;IF(WBS!C51&lt;&gt;"", " "&amp;WBS!C51, "")&amp;IF(WBS!D51&lt;&gt;"", " "&amp;WBS!D51, "")</f>
-        <v/>
-      </c>
-      <c r="C51">
-        <f>WBS!L51</f>
-        <v/>
-      </c>
-      <c r="D51">
-        <f>WBS!M51</f>
-        <v/>
-      </c>
-      <c r="T51" s="14" t="n"/>
-      <c r="U51" s="14" t="n"/>
-      <c r="V51" s="14" t="n"/>
-      <c r="W51" s="14" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <f>WBS!A52</f>
-        <v/>
-      </c>
-      <c r="B52">
-        <f>WBS!B52&amp;IF(WBS!C52&lt;&gt;"", " "&amp;WBS!C52, "")&amp;IF(WBS!D52&lt;&gt;"", " "&amp;WBS!D52, "")</f>
-        <v/>
-      </c>
-      <c r="C52">
-        <f>WBS!L52</f>
-        <v/>
-      </c>
-      <c r="D52">
-        <f>WBS!M52</f>
-        <v/>
-      </c>
-      <c r="W52" s="14" t="n"/>
-      <c r="X52" s="14" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <f>WBS!A53</f>
-        <v/>
-      </c>
-      <c r="B53">
-        <f>WBS!B53&amp;IF(WBS!C53&lt;&gt;"", " "&amp;WBS!C53, "")&amp;IF(WBS!D53&lt;&gt;"", " "&amp;WBS!D53, "")</f>
-        <v/>
-      </c>
-      <c r="C53">
-        <f>WBS!L53</f>
-        <v/>
-      </c>
-      <c r="D53">
-        <f>WBS!M53</f>
-        <v/>
-      </c>
-      <c r="X53" s="14" t="n"/>
-      <c r="Y53" s="14" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <f>WBS!A54</f>
-        <v/>
-      </c>
-      <c r="B54">
-        <f>WBS!B54&amp;IF(WBS!C54&lt;&gt;"", " "&amp;WBS!C54, "")&amp;IF(WBS!D54&lt;&gt;"", " "&amp;WBS!D54, "")</f>
-        <v/>
-      </c>
-      <c r="C54">
-        <f>WBS!L54</f>
-        <v/>
-      </c>
-      <c r="D54">
-        <f>WBS!M54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <f>WBS!A55</f>
-        <v/>
-      </c>
-      <c r="B55">
-        <f>WBS!B55&amp;IF(WBS!C55&lt;&gt;"", " "&amp;WBS!C55, "")&amp;IF(WBS!D55&lt;&gt;"", " "&amp;WBS!D55, "")</f>
-        <v/>
-      </c>
-      <c r="C55">
-        <f>WBS!L55</f>
-        <v/>
-      </c>
-      <c r="D55">
-        <f>WBS!M55</f>
-        <v/>
-      </c>
-      <c r="Y55" s="14" t="n"/>
-      <c r="Z55" s="14" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <f>WBS!A56</f>
-        <v/>
-      </c>
-      <c r="B56">
-        <f>WBS!B56&amp;IF(WBS!C56&lt;&gt;"", " "&amp;WBS!C56, "")&amp;IF(WBS!D56&lt;&gt;"", " "&amp;WBS!D56, "")</f>
-        <v/>
-      </c>
-      <c r="C56">
-        <f>WBS!L56</f>
-        <v/>
-      </c>
-      <c r="D56">
-        <f>WBS!M56</f>
-        <v/>
-      </c>
-      <c r="Z56" s="15" t="n"/>
-      <c r="AA56" s="15" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <f>WBS!A57</f>
-        <v/>
-      </c>
-      <c r="B57">
-        <f>WBS!B57&amp;IF(WBS!C57&lt;&gt;"", " "&amp;WBS!C57, "")&amp;IF(WBS!D57&lt;&gt;"", " "&amp;WBS!D57, "")</f>
-        <v/>
-      </c>
-      <c r="C57">
-        <f>WBS!L57</f>
-        <v/>
-      </c>
-      <c r="D57">
-        <f>WBS!M57</f>
-        <v/>
-      </c>
-      <c r="Z57" s="14" t="n"/>
-      <c r="AA57" s="14" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <f>WBS!A58</f>
-        <v/>
-      </c>
-      <c r="B58">
-        <f>WBS!B58&amp;IF(WBS!C58&lt;&gt;"", " "&amp;WBS!C58, "")&amp;IF(WBS!D58&lt;&gt;"", " "&amp;WBS!D58, "")</f>
-        <v/>
-      </c>
-      <c r="C58">
-        <f>WBS!L58</f>
-        <v/>
-      </c>
-      <c r="D58">
-        <f>WBS!M58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <f>WBS!A59</f>
-        <v/>
-      </c>
-      <c r="B59">
-        <f>WBS!B59&amp;IF(WBS!C59&lt;&gt;"", " "&amp;WBS!C59, "")&amp;IF(WBS!D59&lt;&gt;"", " "&amp;WBS!D59, "")</f>
-        <v/>
-      </c>
-      <c r="C59">
-        <f>WBS!L59</f>
-        <v/>
-      </c>
-      <c r="D59">
-        <f>WBS!M59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <f>WBS!A60</f>
-        <v/>
-      </c>
-      <c r="B60">
-        <f>WBS!B60&amp;IF(WBS!C60&lt;&gt;"", " "&amp;WBS!C60, "")&amp;IF(WBS!D60&lt;&gt;"", " "&amp;WBS!D60, "")</f>
-        <v/>
-      </c>
-      <c r="C60">
-        <f>WBS!L60</f>
-        <v/>
-      </c>
-      <c r="D60">
-        <f>WBS!M60</f>
-        <v/>
-      </c>
-      <c r="AA60" s="14" t="n"/>
-      <c r="AB60" s="14" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <f>WBS!A61</f>
-        <v/>
-      </c>
-      <c r="B61">
-        <f>WBS!B61&amp;IF(WBS!C61&lt;&gt;"", " "&amp;WBS!C61, "")&amp;IF(WBS!D61&lt;&gt;"", " "&amp;WBS!D61, "")</f>
-        <v/>
-      </c>
-      <c r="C61">
-        <f>WBS!L61</f>
-        <v/>
-      </c>
-      <c r="D61">
-        <f>WBS!M61</f>
-        <v/>
-      </c>
-      <c r="AB61" s="14" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <f>WBS!A62</f>
-        <v/>
-      </c>
-      <c r="B62">
-        <f>WBS!B62&amp;IF(WBS!C62&lt;&gt;"", " "&amp;WBS!C62, "")&amp;IF(WBS!D62&lt;&gt;"", " "&amp;WBS!D62, "")</f>
-        <v/>
-      </c>
-      <c r="C62">
-        <f>WBS!L62</f>
-        <v/>
-      </c>
-      <c r="D62">
-        <f>WBS!M62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <f>WBS!A63</f>
-        <v/>
-      </c>
-      <c r="B63">
-        <f>WBS!B63&amp;IF(WBS!C63&lt;&gt;"", " "&amp;WBS!C63, "")&amp;IF(WBS!D63&lt;&gt;"", " "&amp;WBS!D63, "")</f>
-        <v/>
-      </c>
-      <c r="C63">
-        <f>WBS!L63</f>
-        <v/>
-      </c>
-      <c r="D63">
-        <f>WBS!M63</f>
-        <v/>
-      </c>
-      <c r="AB63" s="14" t="n"/>
-      <c r="AC63" s="14" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <f>WBS!A64</f>
-        <v/>
-      </c>
-      <c r="B64">
-        <f>WBS!B64&amp;IF(WBS!C64&lt;&gt;"", " "&amp;WBS!C64, "")&amp;IF(WBS!D64&lt;&gt;"", " "&amp;WBS!D64, "")</f>
-        <v/>
-      </c>
-      <c r="C64">
-        <f>WBS!L64</f>
-        <v/>
-      </c>
-      <c r="D64">
-        <f>WBS!M64</f>
-        <v/>
-      </c>
-      <c r="AC64" s="14" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <f>WBS!A65</f>
-        <v/>
-      </c>
-      <c r="B65">
-        <f>WBS!B65&amp;IF(WBS!C65&lt;&gt;"", " "&amp;WBS!C65, "")&amp;IF(WBS!D65&lt;&gt;"", " "&amp;WBS!D65, "")</f>
-        <v/>
-      </c>
-      <c r="C65">
-        <f>WBS!L65</f>
-        <v/>
-      </c>
-      <c r="D65">
-        <f>WBS!M65</f>
-        <v/>
-      </c>
-      <c r="AC65" s="14" t="n"/>
-      <c r="AD65" s="14" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <f>WBS!A66</f>
-        <v/>
-      </c>
-      <c r="B66">
-        <f>WBS!B66&amp;IF(WBS!C66&lt;&gt;"", " "&amp;WBS!C66, "")&amp;IF(WBS!D66&lt;&gt;"", " "&amp;WBS!D66, "")</f>
-        <v/>
-      </c>
-      <c r="C66">
-        <f>WBS!L66</f>
-        <v/>
-      </c>
-      <c r="D66">
-        <f>WBS!M66</f>
-        <v/>
-      </c>
-      <c r="AD66" s="14" t="n"/>
-      <c r="AE66" s="14" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>Critical Path</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>1.1.1 → 1.1.2 → 1.2.1 → 2.1.1 → 2.1.2 → 2.1.3 → 3.1.1 → 3.1.2 → 3.2.1 → 3.2.2 → 4.1.1 → 4.1.2 → 4.1.3 → 4.2.1 → 4.2.3 → 5.1.1 → 5.1.2 → 5.1.3 → 5.2.1 → 5.2.3 → 6.1.1 → 6.1.2 → 6.1.3 → 6.2.1 → 6.2.3 → 7.1.1 → 7.1.2 → 7.2.1 → 7.2.2 → 7.2.3 → 7.2.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>Total PERT Duration</t>
-        </is>
-      </c>
-      <c r="B69">
-        <f>WBS!L67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="16" t="inlineStr">
-        <is>
-          <t>CI 68%</t>
-        </is>
-      </c>
-      <c r="B70">
-        <f>WBS!L67&amp;" ± "&amp;WBS!M67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="16" t="inlineStr">
-        <is>
-          <t>CI 95%</t>
-        </is>
-      </c>
-      <c r="B71">
-        <f>WBS!L67&amp;" ± 2×"&amp;WBS!M67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="16" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="B72" s="17" t="n">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="16" t="inlineStr">
-        <is>
-          <t>End Date</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="n">
-        <v>46632</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="18" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="14" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Critical Path</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="15" t="inlineStr"/>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Parallel Activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="19" t="inlineStr"/>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Continuous Activity</t>
-        </is>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Weekly TOTAL</t>
+        </is>
+      </c>
+      <c r="D8" s="12">
+        <f>SUM(D3:D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="12">
+        <f>SUM(E3:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="12">
+        <f>SUM(F3:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>SUM(G3:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="12">
+        <f>SUM(H3:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="12">
+        <f>SUM(I3:I7)</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>SUM(J3:J7)</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>SUM(K3:K7)</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>SUM(L3:L7)</f>
+        <v/>
+      </c>
+      <c r="M8" s="12">
+        <f>SUM(M3:M7)</f>
+        <v/>
+      </c>
+      <c r="N8" s="12">
+        <f>SUM(N3:N7)</f>
+        <v/>
+      </c>
+      <c r="O8" s="12">
+        <f>SUM(O3:O7)</f>
+        <v/>
+      </c>
+      <c r="P8" s="12">
+        <f>SUM(P3:P7)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="12">
+        <f>SUM(Q3:Q7)</f>
+        <v/>
+      </c>
+      <c r="R8" s="12">
+        <f>SUM(R3:R7)</f>
+        <v/>
+      </c>
+      <c r="S8" s="12">
+        <f>SUM(S3:S7)</f>
+        <v/>
+      </c>
+      <c r="T8" s="12">
+        <f>SUM(T3:T7)</f>
+        <v/>
+      </c>
+      <c r="U8" s="12">
+        <f>SUM(U3:U7)</f>
+        <v/>
+      </c>
+      <c r="V8" s="12">
+        <f>SUM(V3:V7)</f>
+        <v/>
+      </c>
+      <c r="W8" s="12">
+        <f>SUM(W3:W7)</f>
+        <v/>
+      </c>
+      <c r="X8" s="12">
+        <f>SUM(X3:X7)</f>
+        <v/>
+      </c>
+      <c r="Y8" s="12">
+        <f>SUM(Y3:Y7)</f>
+        <v/>
+      </c>
+      <c r="Z8" s="12">
+        <f>SUM(Z3:Z7)</f>
+        <v/>
+      </c>
+      <c r="AA8" s="12">
+        <f>SUM(AA3:AA7)</f>
+        <v/>
+      </c>
+      <c r="AB8" s="12">
+        <f>SUM(AB3:AB7)</f>
+        <v/>
+      </c>
+      <c r="AC8" s="12">
+        <f>SUM(AC3:AC7)</f>
+        <v/>
+      </c>
+      <c r="AD8" s="12">
+        <f>SUM(AD3:AD7)</f>
+        <v/>
+      </c>
+      <c r="AE8" s="12">
+        <f>SUM(AE3:AE7)</f>
+        <v/>
+      </c>
+      <c r="AF8" s="12">
+        <f>SUM(AF3:AF7)</f>
+        <v/>
+      </c>
+      <c r="AG8" s="12">
+        <f>SUM(AG3:AG7)</f>
+        <v/>
+      </c>
+      <c r="AH8" s="12">
+        <f>SUM(AH3:AH7)</f>
+        <v/>
+      </c>
+      <c r="AI8" s="12">
+        <f>SUM(AI3:AI7)</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="12">
+        <f>SUM(AJ3:AJ7)</f>
+        <v/>
+      </c>
+      <c r="AK8" s="12">
+        <f>SUM(AK3:AK7)</f>
+        <v/>
+      </c>
+      <c r="AL8" s="12">
+        <f>SUM(AL3:AL7)</f>
+        <v/>
+      </c>
+      <c r="AM8" s="12">
+        <f>SUM(AM3:AM7)</f>
+        <v/>
+      </c>
+      <c r="AN8" s="12">
+        <f>SUM(AN3:AN7)</f>
+        <v/>
+      </c>
+      <c r="AO8" s="12">
+        <f>SUM(AO3:AO7)</f>
+        <v/>
+      </c>
+      <c r="AP8" s="12">
+        <f>SUM(AP3:AP7)</f>
+        <v/>
+      </c>
+      <c r="AQ8" s="12">
+        <f>SUM(AQ3:AQ7)</f>
+        <v/>
+      </c>
+      <c r="AR8" s="12">
+        <f>SUM(AR3:AR7)</f>
+        <v/>
+      </c>
+      <c r="AS8" s="12">
+        <f>SUM(AS3:AS7)</f>
+        <v/>
+      </c>
+      <c r="AT8" s="12">
+        <f>SUM(AT3:AT7)</f>
+        <v/>
+      </c>
+      <c r="AU8" s="12">
+        <f>SUM(AU3:AU7)</f>
+        <v/>
+      </c>
+      <c r="AV8" s="12">
+        <f>SUM(AV3:AV7)</f>
+        <v/>
+      </c>
+      <c r="AW8" s="12">
+        <f>SUM(AW3:AW7)</f>
+        <v/>
+      </c>
+      <c r="AX8" s="12">
+        <f>SUM(AX3:AX7)</f>
+        <v/>
+      </c>
+      <c r="AY8" s="12">
+        <f>SUM(AY3:AY7)</f>
+        <v/>
+      </c>
+      <c r="AZ8" s="12">
+        <f>SUM(AZ3:AZ7)</f>
+        <v/>
+      </c>
+      <c r="BA8" s="12">
+        <f>SUM(BA3:BA7)</f>
+        <v/>
+      </c>
+      <c r="BB8" s="12">
+        <f>SUM(D8:BA8)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -6629,1178 +6716,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="D1" s="20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E1" s="20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F1" s="20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G1" s="20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H1" s="20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="B2" s="21" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C2" s="21" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="D2" s="22" t="inlineStr">
-        <is>
-          <t>Cloud Architect</t>
-        </is>
-      </c>
-      <c r="E2" s="22" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="F2" s="22" t="inlineStr">
-        <is>
-          <t>Security Engineer</t>
-        </is>
-      </c>
-      <c r="G2" s="22" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="H2" s="22" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="I2" s="22" t="inlineStr">
-        <is>
-          <t>TOTAL EFFORT</t>
-        </is>
-      </c>
-      <c r="J2" s="22" t="inlineStr">
-        <is>
-          <t>BILLABLE EFFORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Assessment &amp; Discovery</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Inventory and assess current-state infrastructure and application portfolio</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="D3" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="I3" s="24">
-        <f>SUM(D3:H3)</f>
-        <v/>
-      </c>
-      <c r="J3" s="24">
-        <f>SUMPRODUCT(D3:H3,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Assessment &amp; Discovery</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Inventory and assess current-state infrastructure and application portfolio</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="E4" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="24">
-        <f>SUM(D4:H4)</f>
-        <v/>
-      </c>
-      <c r="J4" s="24">
-        <f>SUMPRODUCT(D4:H4,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Assessment &amp; Discovery</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Inventory and assess current-state infrastructure and application portfolio</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" s="24">
-        <f>SUM(D5:H5)</f>
-        <v/>
-      </c>
-      <c r="J5" s="24">
-        <f>SUMPRODUCT(D5:H5,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Assessment &amp; Discovery</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Inventory and assess current-state infrastructure and application portfolio</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="I6" s="24">
-        <f>SUM(D6:H6)</f>
-        <v/>
-      </c>
-      <c r="J6" s="24">
-        <f>SUMPRODUCT(D6:H6,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Cloud Architecture &amp; Planning</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Design the target cloud architecture and produce the detailed migration plan</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I7" s="24">
-        <f>SUM(D7:H7)</f>
-        <v/>
-      </c>
-      <c r="J7" s="24">
-        <f>SUMPRODUCT(D7:H7,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Cloud Architecture &amp; Planning</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Design the target cloud architecture and produce the detailed migration plan</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" s="24">
-        <f>SUM(D8:H8)</f>
-        <v/>
-      </c>
-      <c r="J8" s="24">
-        <f>SUMPRODUCT(D8:H8,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Cloud Architecture &amp; Planning</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Design the target cloud architecture and produce the detailed migration plan</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="I9" s="24">
-        <f>SUM(D9:H9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="24">
-        <f>SUMPRODUCT(D9:H9,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Cloud Architecture &amp; Planning</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Design the target cloud architecture and produce the detailed migration plan</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="I10" s="24">
-        <f>SUM(D10:H10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="24">
-        <f>SUMPRODUCT(D10:H10,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Infrastructure Setup</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Provision and configure the target cloud landing zone and platform services</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" s="24">
-        <f>SUM(D11:H11)</f>
-        <v/>
-      </c>
-      <c r="J11" s="24">
-        <f>SUMPRODUCT(D11:H11,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Infrastructure Setup</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Provision and configure the target cloud landing zone and platform services</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="I12" s="24">
-        <f>SUM(D12:H12)</f>
-        <v/>
-      </c>
-      <c r="J12" s="24">
-        <f>SUMPRODUCT(D12:H12,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Infrastructure Setup</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Provision and configure the target cloud landing zone and platform services</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="I13" s="24">
-        <f>SUM(D13:H13)</f>
-        <v/>
-      </c>
-      <c r="J13" s="24">
-        <f>SUMPRODUCT(D13:H13,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Infrastructure Setup</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Provision and configure the target cloud landing zone and platform services</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="I14" s="24">
-        <f>SUM(D14:H14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="24">
-        <f>SUMPRODUCT(D14:H14,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 1</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 lower-complexity applications to the cloud environment</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" s="24">
-        <f>SUM(D15:H15)</f>
-        <v/>
-      </c>
-      <c r="J15" s="24">
-        <f>SUMPRODUCT(D15:H15,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 1</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 lower-complexity applications to the cloud environment</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="I16" s="24">
-        <f>SUM(D16:H16)</f>
-        <v/>
-      </c>
-      <c r="J16" s="24">
-        <f>SUMPRODUCT(D16:H16,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 1</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 lower-complexity applications to the cloud environment</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="I17" s="24">
-        <f>SUM(D17:H17)</f>
-        <v/>
-      </c>
-      <c r="J17" s="24">
-        <f>SUMPRODUCT(D17:H17,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 1</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 lower-complexity applications to the cloud environment</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="I18" s="24">
-        <f>SUM(D18:H18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="24">
-        <f>SUMPRODUCT(D18:H18,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 2</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 medium-complexity applications to the cloud environment</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="I19" s="24">
-        <f>SUM(D19:H19)</f>
-        <v/>
-      </c>
-      <c r="J19" s="24">
-        <f>SUMPRODUCT(D19:H19,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 2</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 medium-complexity applications to the cloud environment</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="I20" s="24">
-        <f>SUM(D20:H20)</f>
-        <v/>
-      </c>
-      <c r="J20" s="24">
-        <f>SUMPRODUCT(D20:H20,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 2</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 medium-complexity applications to the cloud environment</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="I21" s="24">
-        <f>SUM(D21:H21)</f>
-        <v/>
-      </c>
-      <c r="J21" s="24">
-        <f>SUMPRODUCT(D21:H21,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 2</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 medium-complexity applications to the cloud environment</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="G22" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="24">
-        <f>SUM(D22:H22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="24">
-        <f>SUMPRODUCT(D22:H22,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 3</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 high-complexity, business-critical applications to cloud</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="I23" s="24">
-        <f>SUM(D23:H23)</f>
-        <v/>
-      </c>
-      <c r="J23" s="24">
-        <f>SUMPRODUCT(D23:H23,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 3</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 high-complexity, business-critical applications to cloud</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="I24" s="24">
-        <f>SUM(D24:H24)</f>
-        <v/>
-      </c>
-      <c r="J24" s="24">
-        <f>SUMPRODUCT(D24:H24,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 3</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 high-complexity, business-critical applications to cloud</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="I25" s="24">
-        <f>SUM(D25:H25)</f>
-        <v/>
-      </c>
-      <c r="J25" s="24">
-        <f>SUMPRODUCT(D25:H25,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 3</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 high-complexity, business-critical applications to cloud</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="G26" s="23" t="n">
-        <v>45</v>
-      </c>
-      <c r="I26" s="24">
-        <f>SUM(D26:H26)</f>
-        <v/>
-      </c>
-      <c r="J26" s="24">
-        <f>SUMPRODUCT(D26:H26,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Testing, Validation &amp; Cutover</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>System-wide non-functional testing, UAT, production cutover and hypercare stabilisation</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="I27" s="24">
-        <f>SUM(D27:H27)</f>
-        <v/>
-      </c>
-      <c r="J27" s="24">
-        <f>SUMPRODUCT(D27:H27,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Testing, Validation &amp; Cutover</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>System-wide non-functional testing, UAT, production cutover and hypercare stabilisation</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="I28" s="24">
-        <f>SUM(D28:H28)</f>
-        <v/>
-      </c>
-      <c r="J28" s="24">
-        <f>SUMPRODUCT(D28:H28,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Testing, Validation &amp; Cutover</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>System-wide non-functional testing, UAT, production cutover and hypercare stabilisation</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="I29" s="24">
-        <f>SUM(D29:H29)</f>
-        <v/>
-      </c>
-      <c r="J29" s="24">
-        <f>SUMPRODUCT(D29:H29,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Testing, Validation &amp; Cutover</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>System-wide non-functional testing, UAT, production cutover and hypercare stabilisation</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="I30" s="24">
-        <f>SUM(D30:H30)</f>
-        <v/>
-      </c>
-      <c r="J30" s="24">
-        <f>SUMPRODUCT(D30:H30,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Subtotal — Technical</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="D31" s="25">
-        <f>SUM(D3,D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D23,D24,D25,D26,D27,D28,D29,D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="25">
-        <f>SUM(E3,E4,E5,E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E23,E24,E25,E26,E27,E28,E29,E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="25">
-        <f>SUM(F3,F4,F5,F6,F7,F8,F9,F10,F11,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F23,F24,F25,F26,F27,F28,F29,F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="25">
-        <f>SUM(G3,G4,G5,G6,G7,G8,G9,G10,G11,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30)</f>
-        <v/>
-      </c>
-      <c r="H31" s="25">
-        <f>SUM(H3,H4,H5,H6,H7,H8,H9,H10,H11,H12,H13,H14,H15,H16,H17,H18,H19,H20,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30)</f>
-        <v/>
-      </c>
-      <c r="I31" s="26">
-        <f>SUM(D31:H31)</f>
-        <v/>
-      </c>
-      <c r="J31" s="26">
-        <f>SUMPRODUCT(D31:H31,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Assessment &amp; Discovery</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Inventory and assess current-state infrastructure and application portfolio</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="H32" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="I32" s="24">
-        <f>SUM(D32:H32)</f>
-        <v/>
-      </c>
-      <c r="J32" s="24">
-        <f>SUMPRODUCT(D32:H32,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Cloud Architecture &amp; Planning</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Design the target cloud architecture and produce the detailed migration plan</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="H33" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="I33" s="24">
-        <f>SUM(D33:H33)</f>
-        <v/>
-      </c>
-      <c r="J33" s="24">
-        <f>SUMPRODUCT(D33:H33,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Infrastructure Setup</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Provision and configure the target cloud landing zone and platform services</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="H34" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="I34" s="24">
-        <f>SUM(D34:H34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="24">
-        <f>SUMPRODUCT(D34:H34,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 1</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 lower-complexity applications to the cloud environment</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="H35" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="I35" s="24">
-        <f>SUM(D35:H35)</f>
-        <v/>
-      </c>
-      <c r="J35" s="24">
-        <f>SUMPRODUCT(D35:H35,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 2</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 medium-complexity applications to the cloud environment</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="H36" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="I36" s="24">
-        <f>SUM(D36:H36)</f>
-        <v/>
-      </c>
-      <c r="J36" s="24">
-        <f>SUMPRODUCT(D36:H36,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Migration Wave 3</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Migrate 4 high-complexity, business-critical applications to cloud</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="H37" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="I37" s="24">
-        <f>SUM(D37:H37)</f>
-        <v/>
-      </c>
-      <c r="J37" s="24">
-        <f>SUMPRODUCT(D37:H37,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Testing, Validation &amp; Cutover</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>System-wide non-functional testing, UAT, production cutover and hypercare stabilisation</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="H38" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="I38" s="24">
-        <f>SUM(D38:H38)</f>
-        <v/>
-      </c>
-      <c r="J38" s="24">
-        <f>SUMPRODUCT(D38:H38,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Subtotal — Management</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr"/>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="D39" s="25">
-        <f>SUM(D32,D33,D34,D35,D36,D37,D38)</f>
-        <v/>
-      </c>
-      <c r="E39" s="25">
-        <f>SUM(E32,E33,E34,E35,E36,E37,E38)</f>
-        <v/>
-      </c>
-      <c r="F39" s="25">
-        <f>SUM(F32,F33,F34,F35,F36,F37,F38)</f>
-        <v/>
-      </c>
-      <c r="G39" s="25">
-        <f>SUM(G32,G33,G34,G35,G36,G37,G38)</f>
-        <v/>
-      </c>
-      <c r="H39" s="25">
-        <f>SUM(H32,H33,H34,H35,H36,H37,H38)</f>
-        <v/>
-      </c>
-      <c r="I39" s="26">
-        <f>SUM(D39:H39)</f>
-        <v/>
-      </c>
-      <c r="J39" s="26">
-        <f>SUMPRODUCT(D39:H39,(D$1:H$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr"/>
-      <c r="C40" s="11" t="inlineStr"/>
-      <c r="I40" s="27">
-        <f>SUM(I31,I39)</f>
-        <v/>
-      </c>
-      <c r="J40" s="27">
-        <f>SUM(J31,J39)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7892,291 +6807,291 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>R01</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>Cloud Architect resource unavailability due to market competition</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>Organizational</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>1, 2, 3</t>
         </is>
       </c>
-      <c r="E2" s="28" t="n">
+      <c r="E2" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="28" t="n">
+      <c r="F2" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="19">
         <f>E2*F2</f>
         <v/>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="19">
         <f>IF(G2&gt;=15,"CRITICAL",IF(G2&gt;=10,"HIGH",IF(G2&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I2" s="28" t="inlineStr">
+      <c r="I2" s="19" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="J2" s="19" t="inlineStr">
         <is>
           <t>Dual-source cloud architects; include bench resource in contract; knowledge redundancy through pair working</t>
         </is>
       </c>
-      <c r="K2" s="28" t="inlineStr">
+      <c r="K2" s="19" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="L2" s="28" t="n">
+      <c r="L2" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="M2" s="28">
+      <c r="M2" s="19">
         <f>L2*650</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>R02</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>Application dependency complexity exceeds initial assessment estimates</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>1, 2</t>
         </is>
       </c>
-      <c r="E3" s="28" t="n">
+      <c r="E3" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="28" t="n">
+      <c r="F3" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="19">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="19">
         <f>IF(G3&gt;=15,"CRITICAL",IF(G3&gt;=10,"HIGH",IF(G3&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J3" s="28" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>Automated dependency scanning tools; allow buffer time in assessment phase; iterative discovery</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="L3" s="28" t="n">
+      <c r="L3" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="M3" s="28">
+      <c r="M3" s="19">
         <f>L3*650</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>R03</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Data migration volume or quality issues causing delays</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>4, 5, 6</t>
         </is>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="E4" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="19">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="19">
         <f>IF(G4&gt;=15,"CRITICAL",IF(G4&gt;=10,"HIGH",IF(G4&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I4" s="28" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J4" s="28" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>Early data profiling; automated data quality scripts; dry-run migrations before production cutover</t>
         </is>
       </c>
-      <c r="K4" s="28" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="L4" s="28" t="n">
+      <c r="L4" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="19">
         <f>L4*650</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>R04</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Legacy application incompatibility with containerisation approach</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>4, 5, 6, 7</t>
         </is>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="19">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="19">
         <f>IF(G5&gt;=15,"CRITICAL",IF(G5&gt;=10,"HIGH",IF(G5&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I5" s="28" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J5" s="28" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>Technical spike in Phase 1; fallback to VM-based lift-and-shift for incompatible apps; 6-R reclassification</t>
         </is>
       </c>
-      <c r="K5" s="28" t="inlineStr">
+      <c r="K5" s="19" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="L5" s="28" t="n">
+      <c r="L5" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="M5" s="28">
+      <c r="M5" s="19">
         <f>L5*650</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>R05</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Cloud provider service outage or degradation during active migration window</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>3, 4, 7</t>
         </is>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="19">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="19">
         <f>IF(G6&gt;=15,"CRITICAL",IF(G6&gt;=10,"HIGH",IF(G6&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="19" t="inlineStr">
         <is>
           <t>Monitor cloud provider status page; schedule cutover windows during low-risk periods; multi-region failover design</t>
         </is>
       </c>
-      <c r="K6" s="28" t="inlineStr">
+      <c r="K6" s="19" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="L6" s="28" t="n">
+      <c r="L6" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="28">
+      <c r="M6" s="19">
         <f>L6*650</f>
         <v/>
       </c>
@@ -8588,59 +7503,59 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>R13</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Inadequate rollback capability for Wave 3 critical applications</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>6, 7</t>
         </is>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="19">
         <f>E14*F14</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="19">
         <f>IF(G14&gt;=15,"CRITICAL",IF(G14&gt;=10,"HIGH",IF(G14&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="19" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" s="19" t="inlineStr">
         <is>
           <t>Full rollback plan tested in rehearsal; parallel-run mode for critical apps before DNS cutover; data replication maintained</t>
         </is>
       </c>
-      <c r="K14" s="28" t="inlineStr">
+      <c r="K14" s="19" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="L14" s="28" t="n">
+      <c r="L14" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="M14" s="28">
+      <c r="M14" s="19">
         <f>L14*650</f>
         <v/>
       </c>
@@ -8783,11 +7698,11 @@
         </is>
       </c>
       <c r="L19">
-        <f>L18*0.2</f>
+        <f>(WBS!H67*(1+0.1+0.05)+L18)*0.2</f>
         <v/>
       </c>
       <c r="M19">
-        <f>M18*0.2</f>
+        <f>(WBS!H67*(1+0.1+0.05)+L18)*0.2*650</f>
         <v/>
       </c>
     </row>
@@ -8796,17 +7711,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -9251,7 +8166,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Total PERT Effort (pd)</t>
+          <t>Tech PERT Effort (PD)</t>
         </is>
       </c>
       <c r="B11">
@@ -9262,140 +8177,176 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total Billable Effort (pd)</t>
+          <t>PM Overhead (+10%) (PD)</t>
         </is>
       </c>
       <c r="B12">
-        <f>WBS!S67</f>
+        <f>B11*0.1</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Billable Ratio</t>
+          <t>DevOps Overhead (+5%) (PD)</t>
         </is>
       </c>
       <c r="B13">
-        <f>B12/B11</f>
+        <f>B11*0.05</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>σ Total Duration</t>
+          <t>Subtotal Tech + Overhead (PD)</t>
         </is>
       </c>
       <c r="B14">
-        <f>SQRT(SUMPRODUCT(K2:K8,K2:K8))</f>
+        <f>B11+B12+B13</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CI 68% Lower</t>
+          <t>Contingency per-risk (PD)</t>
         </is>
       </c>
       <c r="B15">
-        <f>J9-B14</f>
+        <f>Risks!L18</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CI 68% Upper</t>
+          <t>Low Band</t>
         </is>
       </c>
       <c r="B16">
-        <f>J9+B14</f>
+        <f>B14+B15</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CI 95% Lower</t>
+          <t>Management Reserve (20%) (PD)</t>
         </is>
       </c>
       <c r="B17">
-        <f>J9-2*B14</f>
+        <f>B16*0.2</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CI 95% Upper</t>
+          <t>Medium Band (recommended)</t>
         </is>
       </c>
       <c r="B18">
-        <f>J9+2*B14</f>
+        <f>B16+B17</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Total Contingency</t>
+          <t>High Band</t>
         </is>
       </c>
       <c r="B19">
-        <f>Risks!L18</f>
+        <f>B18*(1+0.12)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Management Reserve</t>
+          <t>Total Billable Effort (PD)</t>
         </is>
       </c>
       <c r="B20">
-        <f>Risks!L19</f>
+        <f>WBS!S67</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Adjusted PERT Effort (pd)</t>
+          <t>Billable Ratio</t>
         </is>
       </c>
       <c r="B21">
-        <f>B11+B19+B20</f>
+        <f>B20/B11</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>Effort by Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Calendar Duration (weeks)</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Effort by Team (PD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="B24">
-        <f>Resources!I31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="B25">
-        <f>Resources!I39</f>
-        <v/>
+      <c r="B27" s="17" t="n">
+        <v>303.3333333333333</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Sensitivity Scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Optimistic: ~85% of Fascia MEDIA — best-case execution for 4-cloud-migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Realistic: Fascia MEDIA — current best estimate including overhead and MR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Pessimistic: ~115% of Fascia MEDIA — material slippage on critical path</t>
+        </is>
       </c>
     </row>
   </sheetData>
